--- a/Britannia Inds.xlsx
+++ b/Britannia Inds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\varun gowda\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8496651-335F-40B3-9440-31AD71F41AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49B6C0AD-595C-4DFD-A14E-EDF4BF5049CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profit &amp; Loss" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,11 @@
     <sheet name="Cash Flow" sheetId="4" r:id="rId3"/>
     <sheet name="assumption" sheetId="5" r:id="rId4"/>
     <sheet name="Data Sheet" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet7" sheetId="13" r:id="rId6"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
   <definedNames>
     <definedName name="UPDATE">'Data Sheet'!$E$1</definedName>
   </definedNames>
@@ -43,8 +47,52 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="B32" authorId="0" shapeId="0" xr:uid="{3F430555-F296-4E03-8A93-F75AC4E98028}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAAAccCPVgc
+kenji    (2022-07-02 07:51:37)
+Industry Growth Rate</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0" shapeId="0" xr:uid="{BE0131C5-0E8D-4502-B03F-ACDF1980FBB0}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAAAccCPVgg
+kenji    (2022-07-02 07:51:37)
+Source: Company 10k filing</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="129">
   <si>
     <t>COMPANY NAME</t>
   </si>
@@ -296,19 +344,158 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>D&amp;A</t>
+  </si>
+  <si>
+    <t>WACC</t>
+  </si>
+  <si>
+    <t>Key Assumptions</t>
+  </si>
+  <si>
+    <t>WACC Calculation</t>
+  </si>
+  <si>
+    <t>Risk-free rate</t>
+  </si>
+  <si>
+    <t>Cost of equity</t>
+  </si>
+  <si>
+    <t>Equity risk premium</t>
+  </si>
+  <si>
+    <t>After-tax cost of debt</t>
+  </si>
+  <si>
+    <t>Beta</t>
+  </si>
+  <si>
+    <t>Equity weight</t>
+  </si>
+  <si>
+    <t>Pre-tax cost of debt</t>
+  </si>
+  <si>
+    <t>Debt weight</t>
+  </si>
+  <si>
+    <t>Tax rate</t>
+  </si>
+  <si>
+    <t>Market capitalization (₹ Cr)</t>
+  </si>
+  <si>
+    <t>Debt (₹ Cr)</t>
+  </si>
+  <si>
+    <t>Cash &amp; equivalents (₹ Cr)</t>
+  </si>
+  <si>
+    <t>Terminal growth rate</t>
+  </si>
+  <si>
+    <t>FCFF Forecast</t>
+  </si>
+  <si>
+    <t>EBIT margin</t>
+  </si>
+  <si>
+    <t>EBIT</t>
+  </si>
+  <si>
+    <t>NOPAT</t>
+  </si>
+  <si>
+    <t>Capex</t>
+  </si>
+  <si>
+    <t>Δ Working Capital</t>
+  </si>
+  <si>
+    <t>FCFF</t>
+  </si>
+  <si>
+    <t>Discount factor</t>
+  </si>
+  <si>
+    <t>PV of FCFF</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>FCFF / WACC</t>
+  </si>
+  <si>
+    <t>Terminal growth</t>
+  </si>
+  <si>
+    <t>Base WACC</t>
+  </si>
+  <si>
+    <t>Base DCF/share</t>
+  </si>
+  <si>
+    <t>BRITANNIA INDUSTRIES LTD - DCF VALUATION</t>
+  </si>
+  <si>
+    <t>Growth Rate</t>
+  </si>
+  <si>
+    <t>Implied Share Price Calculation</t>
+  </si>
+  <si>
+    <t>Sum of PV of FCF</t>
+  </si>
+  <si>
+    <t>Terminal Value</t>
+  </si>
+  <si>
+    <t>PV of Terminal Value</t>
+  </si>
+  <si>
+    <t>Enterprise Value</t>
+  </si>
+  <si>
+    <t>(+) Cash</t>
+  </si>
+  <si>
+    <t>(-) Debt</t>
+  </si>
+  <si>
+    <t>(-) Minority Interest</t>
+  </si>
+  <si>
+    <t>Equity Value</t>
+  </si>
+  <si>
+    <t>Diluted Shares Outstanding (mm)</t>
+  </si>
+  <si>
+    <t>Implied Share Price</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-409]mmm\-yy;@"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
+    <numFmt numFmtId="169" formatCode="&quot;₹&quot;#,##0"/>
+    <numFmt numFmtId="170" formatCode="&quot;₹&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -381,8 +568,69 @@
       <name val="Cambria"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -418,8 +666,44 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2A3E68"/>
+        <bgColor rgb="FF2A3E68"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor rgb="FFFFFF99"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -442,6 +726,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -455,7 +759,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -500,15 +804,59 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="11" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="14" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="18" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="60% - Accent1" xfId="3" builtinId="32"/>
@@ -1176,6 +1524,40 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cover Page"/>
+      <sheetName val="Free Cash Flow"/>
+      <sheetName val="Fixed Assets"/>
+      <sheetName val="Net Working Capital"/>
+      <sheetName val="WACC"/>
+      <sheetName val="DCF"/>
+      <sheetName val="Data Source --&gt;"/>
+      <sheetName val="Income Statement"/>
+      <sheetName val="Balance Sheet"/>
+      <sheetName val="Cash Flow Statement"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Annual" displayName="Annual" ref="A3:S19" headerRowCount="0" totalsRowShown="0" headerRowDxfId="23">
   <tableColumns count="19">
@@ -3768,7 +4150,7 @@
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.77734375" bestFit="1" customWidth="1"/>
@@ -4123,7 +4505,6 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="24" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
@@ -4163,7 +4544,7 @@
         <f>'Profit &amp; Loss'!K6/'Profit &amp; Loss'!K4</f>
         <v>0.1835012132151953</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="30" t="s">
         <v>83</v>
       </c>
     </row>
@@ -4190,7 +4571,7 @@
       <c r="B5" s="26">
         <v>0.03</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="30" t="s">
         <v>83</v>
       </c>
     </row>
@@ -4244,16 +4625,16 @@
       <c r="B1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="30" t="str">
+      <c r="E1" s="44" t="str">
         <f>IF(B2&lt;&gt;B3, "A NEW VERSION OF THE WORKSHEET IS AVAILABLE", "")</f>
         <v/>
       </c>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -4262,15 +4643,15 @@
       <c r="B2" s="4">
         <v>2.1</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -6146,4 +6527,1039 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC5C1B4E-0C2C-4BE6-9A01-D61A2EFF733C}">
+  <dimension ref="A1:K62"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" customWidth="1"/>
+    <col min="7" max="10" width="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="47"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="47"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+    </row>
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="33">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="C4" s="31"/>
+      <c r="D4" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="34">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+    </row>
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="33">
+        <v>0.06</v>
+      </c>
+      <c r="C5" s="31"/>
+      <c r="D5" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="34">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+    </row>
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="33">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C6" s="31"/>
+      <c r="D6" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="34">
+        <v>0.999</v>
+      </c>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="33">
+        <v>0.09</v>
+      </c>
+      <c r="C7" s="31"/>
+      <c r="D7" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="34">
+        <v>1E-3</v>
+      </c>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="34">
+        <v>0.24</v>
+      </c>
+      <c r="C8" s="31"/>
+      <c r="D8" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" s="35">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="32">
+        <v>133874.6</v>
+      </c>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="18">
+        <f>('Profit &amp; Loss'!N12/'Profit &amp; Loss'!H12)^(1/7)-1</f>
+        <v>4.1615559391796397E-2</v>
+      </c>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="32">
+        <v>124.56</v>
+      </c>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="32">
+        <v>0</v>
+      </c>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="33">
+        <v>0.04</v>
+      </c>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="31"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="31"/>
+      <c r="B16" s="36">
+        <v>2026</v>
+      </c>
+      <c r="C16" s="36">
+        <v>2027</v>
+      </c>
+      <c r="D16" s="36">
+        <v>2028</v>
+      </c>
+      <c r="E16" s="36">
+        <v>2029</v>
+      </c>
+      <c r="F16" s="36">
+        <v>2030</v>
+      </c>
+      <c r="G16" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="37">
+        <v>19151.599999999999</v>
+      </c>
+      <c r="C17" s="37">
+        <v>20573.8</v>
+      </c>
+      <c r="D17" s="37">
+        <v>22101.599999999999</v>
+      </c>
+      <c r="E17" s="37">
+        <v>23742.799999999999</v>
+      </c>
+      <c r="F17" s="37">
+        <v>25505.9</v>
+      </c>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="37">
+        <v>0.2</v>
+      </c>
+      <c r="C18" s="37">
+        <v>0.2</v>
+      </c>
+      <c r="D18" s="37">
+        <v>0.2</v>
+      </c>
+      <c r="E18" s="37">
+        <v>0.2</v>
+      </c>
+      <c r="F18" s="37">
+        <v>0.2</v>
+      </c>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="37">
+        <v>3514.3</v>
+      </c>
+      <c r="C19" s="37">
+        <v>3775.3</v>
+      </c>
+      <c r="D19" s="37">
+        <v>4055.7</v>
+      </c>
+      <c r="E19" s="37">
+        <v>4356.8</v>
+      </c>
+      <c r="F19" s="37">
+        <v>4680.3999999999996</v>
+      </c>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="37">
+        <v>0.2</v>
+      </c>
+      <c r="C20" s="37">
+        <v>0.2</v>
+      </c>
+      <c r="D20" s="37">
+        <v>0.2</v>
+      </c>
+      <c r="E20" s="37">
+        <v>0.2</v>
+      </c>
+      <c r="F20" s="37">
+        <v>0.2</v>
+      </c>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="37">
+        <f>'Profit &amp; Loss'!K12</f>
+        <v>2533.4899999999998</v>
+      </c>
+      <c r="C21" s="37">
+        <f>'Profit &amp; Loss'!L12</f>
+        <v>2694.8369528805165</v>
+      </c>
+      <c r="D21" s="37">
+        <f>'Profit &amp; Loss'!M12</f>
+        <v>2883.1905533826211</v>
+      </c>
+      <c r="E21" s="37">
+        <f>'Profit &amp; Loss'!N12</f>
+        <v>3088.6692606278666</v>
+      </c>
+      <c r="F21" s="37">
+        <f>'Profit &amp; Loss'!O12</f>
+        <v>3305.2958972732522</v>
+      </c>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="37">
+        <f>'Profit &amp; Loss'!K8</f>
+        <v>336.83</v>
+      </c>
+      <c r="C22" s="37">
+        <f>'Profit &amp; Loss'!L8</f>
+        <v>317.78559999999999</v>
+      </c>
+      <c r="D22" s="37">
+        <f>'Profit &amp; Loss'!M8</f>
+        <v>350.72263352092779</v>
+      </c>
+      <c r="E22" s="37">
+        <f>'Profit &amp; Loss'!N8</f>
+        <v>385.07830954351249</v>
+      </c>
+      <c r="F22" s="37">
+        <f>'Profit &amp; Loss'!O8</f>
+        <v>421.07097142188348</v>
+      </c>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" s="37">
+        <f>B17*assumption!$B$5</f>
+        <v>574.54799999999989</v>
+      </c>
+      <c r="C23" s="37">
+        <f>C17*assumption!$B$5</f>
+        <v>617.21399999999994</v>
+      </c>
+      <c r="D23" s="37">
+        <f>D17*assumption!$B$5</f>
+        <v>663.04799999999989</v>
+      </c>
+      <c r="E23" s="37">
+        <f>E17*assumption!$B$5</f>
+        <v>712.28399999999999</v>
+      </c>
+      <c r="F23" s="37">
+        <f>F17*assumption!$B$5</f>
+        <v>765.17700000000002</v>
+      </c>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="37">
+        <v>-574.5</v>
+      </c>
+      <c r="C24" s="37">
+        <v>-617.20000000000005</v>
+      </c>
+      <c r="D24" s="37">
+        <v>-663</v>
+      </c>
+      <c r="E24" s="37">
+        <v>-712.3</v>
+      </c>
+      <c r="F24" s="37">
+        <v>-765.2</v>
+      </c>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="37">
+        <v>-36.299999999999997</v>
+      </c>
+      <c r="C25" s="37">
+        <v>-42.7</v>
+      </c>
+      <c r="D25" s="37">
+        <v>-45.8</v>
+      </c>
+      <c r="E25" s="37">
+        <v>-49.2</v>
+      </c>
+      <c r="F25" s="37">
+        <v>-52.9</v>
+      </c>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="37">
+        <v>2469.4</v>
+      </c>
+      <c r="C26" s="37">
+        <v>2612.5</v>
+      </c>
+      <c r="D26" s="37">
+        <v>2815.8</v>
+      </c>
+      <c r="E26" s="37">
+        <v>3033.2</v>
+      </c>
+      <c r="F26" s="37">
+        <v>3265.9</v>
+      </c>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="37">
+        <v>1</v>
+      </c>
+      <c r="C27" s="37">
+        <v>2</v>
+      </c>
+      <c r="D27" s="37">
+        <v>3</v>
+      </c>
+      <c r="E27" s="37">
+        <v>4</v>
+      </c>
+      <c r="F27" s="37">
+        <v>5</v>
+      </c>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="37">
+        <f>B26/(1+$E$8)^B27</f>
+        <v>2248.9981785063751</v>
+      </c>
+      <c r="C28" s="37">
+        <f t="shared" ref="C28:F28" si="0">C26/(1+$E$8)^C27</f>
+        <v>2166.9636132594119</v>
+      </c>
+      <c r="D28" s="37">
+        <f t="shared" si="0"/>
+        <v>2127.1336809739678</v>
+      </c>
+      <c r="E28" s="37">
+        <f t="shared" si="0"/>
+        <v>2086.8521775996514</v>
+      </c>
+      <c r="F28" s="37">
+        <f t="shared" si="0"/>
+        <v>2046.4030866013873</v>
+      </c>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="31"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="B30" s="51"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="52" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="58">
+        <f>SUM(B28:F28)</f>
+        <v>10676.350736940794</v>
+      </c>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="31"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="59">
+        <f>E9</f>
+        <v>4.1615559391796397E-2</v>
+      </c>
+      <c r="K32" s="31"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="60">
+        <f>E8</f>
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="31"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="B34" s="58">
+        <f>F26*(1+B32)/(B33-B32)</f>
+        <v>60332.464394844494</v>
+      </c>
+      <c r="D34" s="52"/>
+      <c r="E34" s="53">
+        <f>B42</f>
+        <v>1914.6427195289116</v>
+      </c>
+      <c r="F34" s="54">
+        <f t="shared" ref="F34" si="1">G34-0.5%</f>
+        <v>3.0000000000000002E-2</v>
+      </c>
+      <c r="G34" s="54">
+        <f>H34-0.5%</f>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="H34" s="54">
+        <v>0.04</v>
+      </c>
+      <c r="I34" s="54">
+        <f>H34+0.5%</f>
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="J34" s="54">
+        <f t="shared" ref="J34" si="2">I34+0.5%</f>
+        <v>4.9999999999999996E-2</v>
+      </c>
+      <c r="K34" s="31"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" s="58">
+        <f>B34/(1+B33)^F27</f>
+        <v>37804.140163470431</v>
+      </c>
+      <c r="D35" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="54">
+        <f t="shared" ref="E35" si="3">E36-0.5%</f>
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="F35" s="53">
+        <f t="dataTable" ref="F35:J39" dt2D="1" dtr="1" r1="B32" r2="B33"/>
+        <v>1924.327115189926</v>
+      </c>
+      <c r="G35" s="53">
+        <v>2078.4326849093704</v>
+      </c>
+      <c r="H35" s="53">
+        <v>2264.6435816537</v>
+      </c>
+      <c r="I35" s="53">
+        <v>2494.1593381060125</v>
+      </c>
+      <c r="J35" s="53">
+        <v>2784.0739778352499</v>
+      </c>
+      <c r="K35" s="31"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" s="58">
+        <f>+B35+B31</f>
+        <v>48480.490900411227</v>
+      </c>
+      <c r="D36" s="51"/>
+      <c r="E36" s="54">
+        <f>E37-0.5%</f>
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="F36" s="53">
+        <v>1769.3263541074441</v>
+      </c>
+      <c r="G36" s="56">
+        <v>1896.614684257926</v>
+      </c>
+      <c r="H36" s="56">
+        <v>2047.9196804745372</v>
+      </c>
+      <c r="I36" s="56">
+        <v>2230.7465509029416</v>
+      </c>
+      <c r="J36" s="53">
+        <v>2456.0912981751617</v>
+      </c>
+      <c r="K36" s="31"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" s="61" t="s">
+        <v>123</v>
+      </c>
+      <c r="B37" s="58">
+        <f>'[1]Balance Sheet'!P26</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="51"/>
+      <c r="E37" s="54">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="F37" s="53">
+        <v>1637.929214079031</v>
+      </c>
+      <c r="G37" s="56">
+        <v>1744.5345535292979</v>
+      </c>
+      <c r="H37" s="57">
+        <v>1869.5201239192659</v>
+      </c>
+      <c r="I37" s="56">
+        <v>2018.0878774016808</v>
+      </c>
+      <c r="J37" s="53">
+        <v>2197.6072461929321</v>
+      </c>
+      <c r="K37" s="31"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="61" t="s">
+        <v>124</v>
+      </c>
+      <c r="B38" s="58">
+        <f>'Balance Sheet'!O6</f>
+        <v>1380.28</v>
+      </c>
+      <c r="D38" s="51"/>
+      <c r="E38" s="54">
+        <f>E37+0.5%</f>
+        <v>0.10300000000000001</v>
+      </c>
+      <c r="F38" s="53">
+        <v>1525.2619280441054</v>
+      </c>
+      <c r="G38" s="56">
+        <v>1615.6068937556772</v>
+      </c>
+      <c r="H38" s="56">
+        <v>1720.2923302151182</v>
+      </c>
+      <c r="I38" s="56">
+        <v>1843.0269798572206</v>
+      </c>
+      <c r="J38" s="53">
+        <v>1988.9191105638711</v>
+      </c>
+      <c r="K38" s="31"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" s="61" t="s">
+        <v>125</v>
+      </c>
+      <c r="B39" s="58">
+        <f>'[1]Balance Sheet'!P57</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="51"/>
+      <c r="E39" s="54">
+        <f t="shared" ref="E39" si="4">E38+0.5%</f>
+        <v>0.10800000000000001</v>
+      </c>
+      <c r="F39" s="53">
+        <v>1427.7012066085849</v>
+      </c>
+      <c r="G39" s="53">
+        <v>1505.051377156904</v>
+      </c>
+      <c r="H39" s="53">
+        <v>1593.7765727858593</v>
+      </c>
+      <c r="I39" s="53">
+        <v>1696.5851328003619</v>
+      </c>
+      <c r="J39" s="53">
+        <v>1817.1193066104693</v>
+      </c>
+      <c r="K39" s="31"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" s="62" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" s="63">
+        <f>B36+B37-B38-B39</f>
+        <v>47100.210900411228</v>
+      </c>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" s="64">
+        <v>24.6</v>
+      </c>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
+      <c r="K41" s="31"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="B42" s="66">
+        <f>B40/B41</f>
+        <v>1914.6427195289116</v>
+      </c>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
+      <c r="K42" s="31"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" s="31"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
+    </row>
+    <row r="50" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C50" s="31"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+    </row>
+    <row r="51" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C51" s="31"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="41"/>
+    </row>
+    <row r="52" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="D52" s="41"/>
+      <c r="E52" s="42"/>
+    </row>
+    <row r="53" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C53" s="31"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="42"/>
+    </row>
+    <row r="54" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C54" s="31"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="42"/>
+    </row>
+    <row r="55" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="D55" s="41"/>
+      <c r="E55" s="42"/>
+    </row>
+    <row r="56" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C56" s="31"/>
+      <c r="D56" s="41"/>
+      <c r="E56" s="42"/>
+    </row>
+    <row r="57" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C57" s="31"/>
+      <c r="D57" s="31"/>
+      <c r="E57" s="31"/>
+    </row>
+    <row r="58" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
+    </row>
+    <row r="59" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C59" s="31"/>
+      <c r="D59" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="E59" s="31" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C60" s="31"/>
+      <c r="D60" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="E60" s="39">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="61" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C61" s="31"/>
+      <c r="D61" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="E61" s="39">
+        <v>9.8000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C62" s="31"/>
+      <c r="D62" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="E62" s="40">
+        <v>1962.4164143094899</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="F33:J33"/>
+    <mergeCell ref="D35:D39"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="A15:F15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>